--- a/VLAN List -- AI Seekho -- Sample.xlsx
+++ b/VLAN List -- AI Seekho -- Sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Various Projects\Centralized Database\2026\VLAN Trace\AI Seekho\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0798E1F1-26B0-4E1B-8272-13988F748DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A44E13-F8AB-4FB5-86A9-5294FCFFC335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D559A8D5-89A9-4E11-86E6-0B650AE95C40}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{D559A8D5-89A9-4E11-86E6-0B650AE95C40}"/>
   </bookViews>
   <sheets>
     <sheet name="VLAN DB" sheetId="7" r:id="rId1"/>
@@ -22,10 +22,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">FTTT!$A$1:$B$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">LR!$A$1:$G$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">LR!$A$1:$G$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">OFN!$A$1:$B$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SL!$A$1:$D$102</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'VLAN DB'!$A$1:$G$301</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SL!$A$1:$D$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'VLAN DB'!$A$1:$G$343</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="636">
   <si>
     <t>FTTT</t>
   </si>
@@ -1814,12 +1814,6 @@
     <t>AI1R12_2G</t>
   </si>
   <si>
-    <t>ROM421_2G</t>
-  </si>
-  <si>
-    <t>ROM292_2G</t>
-  </si>
-  <si>
     <t>AI2R01_2G</t>
   </si>
   <si>
@@ -1829,12 +1823,6 @@
     <t>AI1R12_3G</t>
   </si>
   <si>
-    <t>ROM421_3G</t>
-  </si>
-  <si>
-    <t>ROM292_3G</t>
-  </si>
-  <si>
     <t>AI2R01_3G</t>
   </si>
   <si>
@@ -1844,12 +1832,6 @@
     <t>AI1R12_4G</t>
   </si>
   <si>
-    <t>ROM421_4G</t>
-  </si>
-  <si>
-    <t>ROM292_4G</t>
-  </si>
-  <si>
     <t>AI2R01_4G</t>
   </si>
   <si>
@@ -1910,12 +1892,6 @@
     <t>AI1R12</t>
   </si>
   <si>
-    <t>ROM292</t>
-  </si>
-  <si>
-    <t>ROM421</t>
-  </si>
-  <si>
     <t>XHLI20</t>
   </si>
   <si>
@@ -1925,9 +1901,6 @@
     <t>Link127</t>
   </si>
   <si>
-    <t>Link128</t>
-  </si>
-  <si>
     <t>Link129</t>
   </si>
   <si>
@@ -1935,9 +1908,6 @@
   </si>
   <si>
     <t>Link131</t>
-  </si>
-  <si>
-    <t>Link132</t>
   </si>
   <si>
     <t>Link133</t>
@@ -2499,7 +2469,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2512,6 +2482,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2898,7 +2871,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{815B0988-14A5-456C-8EC4-0B80569E1D54}">
-  <dimension ref="A1:G349"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:G343"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -2932,7 +2906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>152</v>
       </c>
@@ -2945,7 +2919,7 @@
         <v>2110</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>153</v>
       </c>
@@ -2958,7 +2932,7 @@
         <v>2121</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>154</v>
       </c>
@@ -2971,7 +2945,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>155</v>
       </c>
@@ -2984,7 +2958,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>156</v>
       </c>
@@ -2997,7 +2971,7 @@
         <v>3110</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>157</v>
       </c>
@@ -3010,7 +2984,7 @@
         <v>3121</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>158</v>
       </c>
@@ -3023,7 +2997,7 @@
         <v>3123</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>159</v>
       </c>
@@ -3036,7 +3010,7 @@
         <v>3129</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>160</v>
       </c>
@@ -3049,7 +3023,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>161</v>
       </c>
@@ -3062,7 +3036,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>162</v>
       </c>
@@ -3075,7 +3049,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>163</v>
       </c>
@@ -3088,7 +3062,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>164</v>
       </c>
@@ -3101,7 +3075,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>165</v>
       </c>
@@ -3114,7 +3088,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>166</v>
       </c>
@@ -3127,7 +3101,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>167</v>
       </c>
@@ -3140,7 +3114,7 @@
         <v>2186</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>168</v>
       </c>
@@ -3153,7 +3127,7 @@
         <v>3186</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>169</v>
       </c>
@@ -3166,7 +3140,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>170</v>
       </c>
@@ -3179,7 +3153,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>171</v>
       </c>
@@ -3192,7 +3166,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>172</v>
       </c>
@@ -3205,7 +3179,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>173</v>
       </c>
@@ -3218,7 +3192,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>174</v>
       </c>
@@ -3231,7 +3205,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>175</v>
       </c>
@@ -3244,7 +3218,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>176</v>
       </c>
@@ -3257,7 +3231,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>177</v>
       </c>
@@ -3270,7 +3244,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>178</v>
       </c>
@@ -3283,7 +3257,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>179</v>
       </c>
@@ -3296,7 +3270,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>180</v>
       </c>
@@ -3309,7 +3283,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>181</v>
       </c>
@@ -3322,7 +3296,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>182</v>
       </c>
@@ -3335,7 +3309,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>183</v>
       </c>
@@ -3348,7 +3322,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>184</v>
       </c>
@@ -3361,7 +3335,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>185</v>
       </c>
@@ -3374,7 +3348,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>186</v>
       </c>
@@ -3387,7 +3361,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>187</v>
       </c>
@@ -3400,7 +3374,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>188</v>
       </c>
@@ -3413,7 +3387,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>189</v>
       </c>
@@ -3426,7 +3400,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>190</v>
       </c>
@@ -3439,7 +3413,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>191</v>
       </c>
@@ -3452,7 +3426,7 @@
         <v>2055</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>192</v>
       </c>
@@ -3465,7 +3439,7 @@
         <v>2105</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>193</v>
       </c>
@@ -3478,7 +3452,7 @@
         <v>2114</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>194</v>
       </c>
@@ -3491,7 +3465,7 @@
         <v>2120</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>195</v>
       </c>
@@ -3504,7 +3478,7 @@
         <v>2122</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>196</v>
       </c>
@@ -3517,7 +3491,7 @@
         <v>2126</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>197</v>
       </c>
@@ -3530,7 +3504,7 @@
         <v>2127</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>198</v>
       </c>
@@ -3543,7 +3517,7 @@
         <v>3004</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>199</v>
       </c>
@@ -3556,7 +3530,7 @@
         <v>3049</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>200</v>
       </c>
@@ -3569,7 +3543,7 @@
         <v>3050</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>201</v>
       </c>
@@ -3582,7 +3556,7 @@
         <v>3051</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>202</v>
       </c>
@@ -3595,7 +3569,7 @@
         <v>3055</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>198</v>
       </c>
@@ -3608,7 +3582,7 @@
         <v>3080</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>203</v>
       </c>
@@ -3621,7 +3595,7 @@
         <v>3105</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>204</v>
       </c>
@@ -3634,7 +3608,7 @@
         <v>3114</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>205</v>
       </c>
@@ -3647,7 +3621,7 @@
         <v>3120</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>206</v>
       </c>
@@ -3660,7 +3634,7 @@
         <v>3122</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>207</v>
       </c>
@@ -3673,7 +3647,7 @@
         <v>3126</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>208</v>
       </c>
@@ -3686,7 +3660,7 @@
         <v>3127</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>209</v>
       </c>
@@ -3699,7 +3673,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>210</v>
       </c>
@@ -3712,7 +3686,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>211</v>
       </c>
@@ -3725,7 +3699,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>212</v>
       </c>
@@ -3738,7 +3712,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>213</v>
       </c>
@@ -3751,7 +3725,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>214</v>
       </c>
@@ -3764,7 +3738,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>215</v>
       </c>
@@ -3777,7 +3751,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>216</v>
       </c>
@@ -3790,7 +3764,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>217</v>
       </c>
@@ -3803,7 +3777,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>218</v>
       </c>
@@ -3816,7 +3790,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>219</v>
       </c>
@@ -3829,7 +3803,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>220</v>
       </c>
@@ -3842,7 +3816,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>221</v>
       </c>
@@ -3855,7 +3829,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>222</v>
       </c>
@@ -3868,7 +3842,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>223</v>
       </c>
@@ -3881,7 +3855,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>224</v>
       </c>
@@ -3894,7 +3868,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>225</v>
       </c>
@@ -3907,7 +3881,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>226</v>
       </c>
@@ -3920,7 +3894,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>227</v>
       </c>
@@ -3933,7 +3907,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>228</v>
       </c>
@@ -3946,7 +3920,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>229</v>
       </c>
@@ -3959,7 +3933,7 @@
         <v>3074</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>230</v>
       </c>
@@ -3972,7 +3946,7 @@
         <v>3075</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>231</v>
       </c>
@@ -3985,7 +3959,7 @@
         <v>3132</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>232</v>
       </c>
@@ -3998,7 +3972,7 @@
         <v>3134</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>233</v>
       </c>
@@ -4011,7 +3985,7 @@
         <v>3146</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>234</v>
       </c>
@@ -4024,7 +3998,7 @@
         <v>3160</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>235</v>
       </c>
@@ -4037,7 +4011,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>236</v>
       </c>
@@ -4050,7 +4024,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>237</v>
       </c>
@@ -4063,7 +4037,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>238</v>
       </c>
@@ -4076,7 +4050,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>239</v>
       </c>
@@ -4089,7 +4063,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>240</v>
       </c>
@@ -4102,7 +4076,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>241</v>
       </c>
@@ -4115,7 +4089,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>242</v>
       </c>
@@ -4128,7 +4102,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>243</v>
       </c>
@@ -4141,7 +4115,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>244</v>
       </c>
@@ -4154,7 +4128,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>245</v>
       </c>
@@ -4167,7 +4141,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>246</v>
       </c>
@@ -4180,7 +4154,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>247</v>
       </c>
@@ -4193,7 +4167,7 @@
         <v>2088</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>248</v>
       </c>
@@ -4206,7 +4180,7 @@
         <v>2096</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>249</v>
       </c>
@@ -4219,7 +4193,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>250</v>
       </c>
@@ -4232,7 +4206,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>251</v>
       </c>
@@ -4245,7 +4219,7 @@
         <v>2152</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>252</v>
       </c>
@@ -4258,7 +4232,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>253</v>
       </c>
@@ -4271,7 +4245,7 @@
         <v>2158</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>254</v>
       </c>
@@ -4284,7 +4258,7 @@
         <v>2159</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>255</v>
       </c>
@@ -4297,7 +4271,7 @@
         <v>2166</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>256</v>
       </c>
@@ -4310,7 +4284,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>257</v>
       </c>
@@ -4323,7 +4297,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>258</v>
       </c>
@@ -4336,7 +4310,7 @@
         <v>2184</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>259</v>
       </c>
@@ -4349,7 +4323,7 @@
         <v>3096</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>260</v>
       </c>
@@ -4362,7 +4336,7 @@
         <v>3125</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>261</v>
       </c>
@@ -4375,7 +4349,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>262</v>
       </c>
@@ -4388,7 +4362,7 @@
         <v>3152</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>263</v>
       </c>
@@ -4401,7 +4375,7 @@
         <v>3154</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>264</v>
       </c>
@@ -4414,7 +4388,7 @@
         <v>3157</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>265</v>
       </c>
@@ -4427,7 +4401,7 @@
         <v>3158</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>266</v>
       </c>
@@ -4440,7 +4414,7 @@
         <v>3159</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>267</v>
       </c>
@@ -4453,7 +4427,7 @@
         <v>3166</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>268</v>
       </c>
@@ -4466,7 +4440,7 @@
         <v>3168</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>269</v>
       </c>
@@ -4479,7 +4453,7 @@
         <v>3175</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>270</v>
       </c>
@@ -4492,7 +4466,7 @@
         <v>3184</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>271</v>
       </c>
@@ -4505,7 +4479,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>272</v>
       </c>
@@ -4518,7 +4492,7 @@
         <v>2073</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>273</v>
       </c>
@@ -4531,7 +4505,7 @@
         <v>2075</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>274</v>
       </c>
@@ -4544,7 +4518,7 @@
         <v>2076</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>275</v>
       </c>
@@ -4557,7 +4531,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>276</v>
       </c>
@@ -4570,7 +4544,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>277</v>
       </c>
@@ -4583,7 +4557,7 @@
         <v>2110</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>278</v>
       </c>
@@ -4596,7 +4570,7 @@
         <v>2113</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>279</v>
       </c>
@@ -4609,7 +4583,7 @@
         <v>2115</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>280</v>
       </c>
@@ -4622,7 +4596,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>281</v>
       </c>
@@ -4635,7 +4609,7 @@
         <v>2117</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>282</v>
       </c>
@@ -4648,7 +4622,7 @@
         <v>2128</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>283</v>
       </c>
@@ -4661,7 +4635,7 @@
         <v>2130</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>284</v>
       </c>
@@ -4674,7 +4648,7 @@
         <v>2131</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>285</v>
       </c>
@@ -4687,7 +4661,7 @@
         <v>2132</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>286</v>
       </c>
@@ -4700,7 +4674,7 @@
         <v>2133</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>287</v>
       </c>
@@ -4713,7 +4687,7 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>288</v>
       </c>
@@ -4726,7 +4700,7 @@
         <v>2135</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>289</v>
       </c>
@@ -4739,7 +4713,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>290</v>
       </c>
@@ -4752,7 +4726,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>291</v>
       </c>
@@ -4765,7 +4739,7 @@
         <v>2139</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>292</v>
       </c>
@@ -4778,7 +4752,7 @@
         <v>2145</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>293</v>
       </c>
@@ -4791,7 +4765,7 @@
         <v>2146</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>294</v>
       </c>
@@ -4804,7 +4778,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>295</v>
       </c>
@@ -4817,7 +4791,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>296</v>
       </c>
@@ -4830,7 +4804,7 @@
         <v>2178</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>297</v>
       </c>
@@ -4843,7 +4817,7 @@
         <v>3072</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>298</v>
       </c>
@@ -4856,7 +4830,7 @@
         <v>3073</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>299</v>
       </c>
@@ -4869,7 +4843,7 @@
         <v>3076</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>300</v>
       </c>
@@ -4882,7 +4856,7 @@
         <v>3078</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>301</v>
       </c>
@@ -4895,7 +4869,7 @@
         <v>3109</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>302</v>
       </c>
@@ -4908,7 +4882,7 @@
         <v>3110</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>303</v>
       </c>
@@ -4921,7 +4895,7 @@
         <v>3113</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>304</v>
       </c>
@@ -4934,7 +4908,7 @@
         <v>3115</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>305</v>
       </c>
@@ -4947,7 +4921,7 @@
         <v>3116</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>306</v>
       </c>
@@ -4960,7 +4934,7 @@
         <v>3117</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>307</v>
       </c>
@@ -4973,7 +4947,7 @@
         <v>3128</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>308</v>
       </c>
@@ -4986,7 +4960,7 @@
         <v>3130</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>309</v>
       </c>
@@ -4999,7 +4973,7 @@
         <v>3131</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>310</v>
       </c>
@@ -5012,7 +4986,7 @@
         <v>3133</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>311</v>
       </c>
@@ -5025,7 +4999,7 @@
         <v>3135</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>312</v>
       </c>
@@ -5038,7 +5012,7 @@
         <v>3136</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>313</v>
       </c>
@@ -5051,7 +5025,7 @@
         <v>3138</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>314</v>
       </c>
@@ -5064,7 +5038,7 @@
         <v>3139</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>315</v>
       </c>
@@ -5077,7 +5051,7 @@
         <v>3145</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>316</v>
       </c>
@@ -5090,7 +5064,7 @@
         <v>3173</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>317</v>
       </c>
@@ -5103,7 +5077,7 @@
         <v>3178</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>318</v>
       </c>
@@ -5116,7 +5090,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>319</v>
       </c>
@@ -5129,7 +5103,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>320</v>
       </c>
@@ -5142,7 +5116,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>321</v>
       </c>
@@ -5155,7 +5129,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>322</v>
       </c>
@@ -5168,7 +5142,7 @@
         <v>3003</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>323</v>
       </c>
@@ -5181,7 +5155,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>324</v>
       </c>
@@ -5194,7 +5168,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>167</v>
       </c>
@@ -5207,7 +5181,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>325</v>
       </c>
@@ -5220,7 +5194,7 @@
         <v>3030</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>168</v>
       </c>
@@ -5233,7 +5207,7 @@
         <v>3034</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>326</v>
       </c>
@@ -5246,7 +5220,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>327</v>
       </c>
@@ -5259,7 +5233,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>328</v>
       </c>
@@ -5272,7 +5246,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>329</v>
       </c>
@@ -5285,7 +5259,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>330</v>
       </c>
@@ -5298,7 +5272,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>331</v>
       </c>
@@ -5311,7 +5285,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>332</v>
       </c>
@@ -5324,7 +5298,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>333</v>
       </c>
@@ -5337,7 +5311,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>334</v>
       </c>
@@ -5350,7 +5324,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>335</v>
       </c>
@@ -5363,7 +5337,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>336</v>
       </c>
@@ -5376,7 +5350,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>337</v>
       </c>
@@ -5389,7 +5363,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>338</v>
       </c>
@@ -5402,7 +5376,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>339</v>
       </c>
@@ -5415,7 +5389,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>340</v>
       </c>
@@ -5428,7 +5402,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>341</v>
       </c>
@@ -5441,7 +5415,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>342</v>
       </c>
@@ -5454,7 +5428,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>343</v>
       </c>
@@ -5467,7 +5441,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>344</v>
       </c>
@@ -5480,7 +5454,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>345</v>
       </c>
@@ -5493,7 +5467,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>346</v>
       </c>
@@ -5506,7 +5480,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>347</v>
       </c>
@@ -5519,7 +5493,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>348</v>
       </c>
@@ -5532,7 +5506,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>349</v>
       </c>
@@ -5545,7 +5519,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>350</v>
       </c>
@@ -5558,7 +5532,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>351</v>
       </c>
@@ -5571,7 +5545,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>352</v>
       </c>
@@ -5584,7 +5558,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>353</v>
       </c>
@@ -5597,7 +5571,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>354</v>
       </c>
@@ -5610,7 +5584,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>355</v>
       </c>
@@ -5623,7 +5597,7 @@
         <v>2038</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>356</v>
       </c>
@@ -5636,7 +5610,7 @@
         <v>2046</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>357</v>
       </c>
@@ -5649,7 +5623,7 @@
         <v>2052</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>358</v>
       </c>
@@ -5662,7 +5636,7 @@
         <v>2058</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>359</v>
       </c>
@@ -5675,7 +5649,7 @@
         <v>2059</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>360</v>
       </c>
@@ -5688,7 +5662,7 @@
         <v>3001</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>361</v>
       </c>
@@ -5701,7 +5675,7 @@
         <v>3002</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>362</v>
       </c>
@@ -5714,7 +5688,7 @@
         <v>3005</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>363</v>
       </c>
@@ -5727,7 +5701,7 @@
         <v>3008</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>364</v>
       </c>
@@ -5740,7 +5714,7 @@
         <v>3010</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>365</v>
       </c>
@@ -5753,7 +5727,7 @@
         <v>3011</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>366</v>
       </c>
@@ -5766,7 +5740,7 @@
         <v>3012</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>367</v>
       </c>
@@ -5779,7 +5753,7 @@
         <v>3013</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>368</v>
       </c>
@@ -5792,7 +5766,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>369</v>
       </c>
@@ -5805,7 +5779,7 @@
         <v>3016</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>370</v>
       </c>
@@ -5818,7 +5792,7 @@
         <v>3020</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>371</v>
       </c>
@@ -5831,7 +5805,7 @@
         <v>3037</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>372</v>
       </c>
@@ -5844,7 +5818,7 @@
         <v>3038</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>373</v>
       </c>
@@ -5857,7 +5831,7 @@
         <v>3046</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>374</v>
       </c>
@@ -5870,7 +5844,7 @@
         <v>3052</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>375</v>
       </c>
@@ -5883,7 +5857,7 @@
         <v>3058</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>376</v>
       </c>
@@ -5896,7 +5870,7 @@
         <v>3059</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>377</v>
       </c>
@@ -5909,7 +5883,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>378</v>
       </c>
@@ -5922,7 +5896,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>379</v>
       </c>
@@ -5935,7 +5909,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>380</v>
       </c>
@@ -5948,7 +5922,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>381</v>
       </c>
@@ -5961,7 +5935,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>382</v>
       </c>
@@ -5974,7 +5948,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>383</v>
       </c>
@@ -5987,7 +5961,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>384</v>
       </c>
@@ -6000,7 +5974,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>385</v>
       </c>
@@ -6013,7 +5987,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>386</v>
       </c>
@@ -6026,7 +6000,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>387</v>
       </c>
@@ -6039,7 +6013,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>388</v>
       </c>
@@ -6052,7 +6026,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>389</v>
       </c>
@@ -6065,7 +6039,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>390</v>
       </c>
@@ -6078,7 +6052,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>391</v>
       </c>
@@ -6091,7 +6065,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>392</v>
       </c>
@@ -6104,7 +6078,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>393</v>
       </c>
@@ -6117,7 +6091,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>394</v>
       </c>
@@ -6130,7 +6104,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>395</v>
       </c>
@@ -6143,7 +6117,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>396</v>
       </c>
@@ -6156,7 +6130,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>397</v>
       </c>
@@ -6169,7 +6143,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>398</v>
       </c>
@@ -6182,7 +6156,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>399</v>
       </c>
@@ -6195,7 +6169,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>400</v>
       </c>
@@ -6208,7 +6182,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>401</v>
       </c>
@@ -6221,7 +6195,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>402</v>
       </c>
@@ -6234,7 +6208,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
         <v>403</v>
       </c>
@@ -6247,7 +6221,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>404</v>
       </c>
@@ -6260,7 +6234,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>405</v>
       </c>
@@ -6273,7 +6247,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>406</v>
       </c>
@@ -6286,7 +6260,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>407</v>
       </c>
@@ -6299,7 +6273,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>408</v>
       </c>
@@ -6312,7 +6286,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>409</v>
       </c>
@@ -6325,7 +6299,7 @@
         <v>2039</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>410</v>
       </c>
@@ -6338,7 +6312,7 @@
         <v>2040</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>411</v>
       </c>
@@ -6351,7 +6325,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>412</v>
       </c>
@@ -6364,7 +6338,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
         <v>413</v>
       </c>
@@ -6377,7 +6351,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>414</v>
       </c>
@@ -6390,7 +6364,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
         <v>415</v>
       </c>
@@ -6403,7 +6377,7 @@
         <v>2055</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
         <v>416</v>
       </c>
@@ -6416,7 +6390,7 @@
         <v>2056</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
         <v>417</v>
       </c>
@@ -6429,7 +6403,7 @@
         <v>3021</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
         <v>418</v>
       </c>
@@ -6442,7 +6416,7 @@
         <v>3022</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
         <v>419</v>
       </c>
@@ -6455,7 +6429,7 @@
         <v>3023</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
         <v>420</v>
       </c>
@@ -6468,7 +6442,7 @@
         <v>3024</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
         <v>421</v>
       </c>
@@ -6481,7 +6455,7 @@
         <v>3025</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
         <v>422</v>
       </c>
@@ -6494,7 +6468,7 @@
         <v>3026</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
         <v>423</v>
       </c>
@@ -6507,7 +6481,7 @@
         <v>3027</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
         <v>424</v>
       </c>
@@ -6520,7 +6494,7 @@
         <v>3028</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
         <v>425</v>
       </c>
@@ -6533,7 +6507,7 @@
         <v>3029</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>426</v>
       </c>
@@ -6546,7 +6520,7 @@
         <v>3031</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>427</v>
       </c>
@@ -6559,7 +6533,7 @@
         <v>3032</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
         <v>428</v>
       </c>
@@ -6572,7 +6546,7 @@
         <v>3033</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
         <v>429</v>
       </c>
@@ -6585,7 +6559,7 @@
         <v>3039</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>430</v>
       </c>
@@ -6598,7 +6572,7 @@
         <v>3040</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>431</v>
       </c>
@@ -6611,7 +6585,7 @@
         <v>3044</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>432</v>
       </c>
@@ -6624,7 +6598,7 @@
         <v>3047</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
         <v>433</v>
       </c>
@@ -6637,7 +6611,7 @@
         <v>3048</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
         <v>434</v>
       </c>
@@ -6650,7 +6624,7 @@
         <v>3049</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
         <v>435</v>
       </c>
@@ -6663,7 +6637,7 @@
         <v>3055</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
         <v>436</v>
       </c>
@@ -6676,7 +6650,7 @@
         <v>3056</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
         <v>437</v>
       </c>
@@ -6689,7 +6663,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>438</v>
       </c>
@@ -6702,7 +6676,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
         <v>439</v>
       </c>
@@ -6715,7 +6689,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
         <v>440</v>
       </c>
@@ -6728,7 +6702,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
         <v>441</v>
       </c>
@@ -6741,7 +6715,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>442</v>
       </c>
@@ -6754,7 +6728,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
         <v>443</v>
       </c>
@@ -6767,7 +6741,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
         <v>444</v>
       </c>
@@ -6780,7 +6754,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
         <v>445</v>
       </c>
@@ -6793,7 +6767,7 @@
         <v>3001</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
         <v>446</v>
       </c>
@@ -6806,7 +6780,7 @@
         <v>3003</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
         <v>447</v>
       </c>
@@ -6819,7 +6793,7 @@
         <v>3010</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
         <v>448</v>
       </c>
@@ -6832,7 +6806,7 @@
         <v>3017</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
         <v>559</v>
       </c>
@@ -6845,7 +6819,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
         <v>560</v>
       </c>
@@ -6858,7 +6832,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
         <v>561</v>
       </c>
@@ -6871,7 +6845,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
         <v>562</v>
       </c>
@@ -6884,7 +6858,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
         <v>563</v>
       </c>
@@ -6897,7 +6871,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
         <v>564</v>
       </c>
@@ -6910,7 +6884,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
         <v>565</v>
       </c>
@@ -6923,7 +6897,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
         <v>566</v>
       </c>
@@ -6936,7 +6910,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
         <v>567</v>
       </c>
@@ -6949,7 +6923,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
         <v>568</v>
       </c>
@@ -6962,7 +6936,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
         <v>569</v>
       </c>
@@ -6975,7 +6949,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
         <v>570</v>
       </c>
@@ -6988,7 +6962,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
         <v>571</v>
       </c>
@@ -7001,7 +6975,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
         <v>572</v>
       </c>
@@ -7014,7 +6988,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
         <v>573</v>
       </c>
@@ -7027,7 +7001,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
         <v>574</v>
       </c>
@@ -7040,7 +7014,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
         <v>575</v>
       </c>
@@ -7053,7 +7027,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
         <v>576</v>
       </c>
@@ -7066,7 +7040,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
         <v>577</v>
       </c>
@@ -7079,7 +7053,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
         <v>578</v>
       </c>
@@ -7092,7 +7066,7 @@
         <v>2113</v>
       </c>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
         <v>579</v>
       </c>
@@ -7105,7 +7079,7 @@
         <v>3015</v>
       </c>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
         <v>580</v>
       </c>
@@ -7118,7 +7092,7 @@
         <v>3016</v>
       </c>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
         <v>581</v>
       </c>
@@ -7131,7 +7105,7 @@
         <v>3017</v>
       </c>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
         <v>582</v>
       </c>
@@ -7144,7 +7118,7 @@
         <v>3018</v>
       </c>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
         <v>583</v>
       </c>
@@ -7157,7 +7131,7 @@
         <v>3025</v>
       </c>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
         <v>584</v>
       </c>
@@ -7170,7 +7144,7 @@
         <v>3030</v>
       </c>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
         <v>585</v>
       </c>
@@ -7183,7 +7157,7 @@
         <v>3031</v>
       </c>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
         <v>586</v>
       </c>
@@ -7196,7 +7170,7 @@
         <v>3111</v>
       </c>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
         <v>587</v>
       </c>
@@ -7209,7 +7183,7 @@
         <v>3113</v>
       </c>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
         <v>588</v>
       </c>
@@ -7232,10 +7206,10 @@
       <c r="E332" s="2"/>
       <c r="F332" s="2"/>
       <c r="G332" s="2">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="333" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
         <v>590</v>
       </c>
@@ -7245,10 +7219,10 @@
       <c r="E333" s="2"/>
       <c r="F333" s="2"/>
       <c r="G333" s="2">
-        <v>1042</v>
-      </c>
-    </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="334" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
         <v>591</v>
       </c>
@@ -7258,7 +7232,7 @@
       <c r="E334" s="2"/>
       <c r="F334" s="2"/>
       <c r="G334" s="2">
-        <v>1100</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.25">
@@ -7271,10 +7245,10 @@
       <c r="E335" s="2"/>
       <c r="F335" s="2"/>
       <c r="G335" s="2">
-        <v>1105</v>
-      </c>
-    </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="336" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
         <v>593</v>
       </c>
@@ -7284,10 +7258,10 @@
       <c r="E336" s="2"/>
       <c r="F336" s="2"/>
       <c r="G336" s="2">
-        <v>2035</v>
-      </c>
-    </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="337" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
         <v>594</v>
       </c>
@@ -7297,7 +7271,7 @@
       <c r="E337" s="2"/>
       <c r="F337" s="2"/>
       <c r="G337" s="2">
-        <v>2038</v>
+        <v>3035</v>
       </c>
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.25">
@@ -7310,10 +7284,10 @@
       <c r="E338" s="2"/>
       <c r="F338" s="2"/>
       <c r="G338" s="2">
-        <v>2042</v>
-      </c>
-    </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="339" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
         <v>596</v>
       </c>
@@ -7323,10 +7297,10 @@
       <c r="E339" s="2"/>
       <c r="F339" s="2"/>
       <c r="G339" s="2">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3105</v>
+      </c>
+    </row>
+    <row r="340" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
         <v>597</v>
       </c>
@@ -7336,10 +7310,10 @@
       <c r="E340" s="2"/>
       <c r="F340" s="2"/>
       <c r="G340" s="2">
-        <v>2105</v>
-      </c>
-    </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="341" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
         <v>598</v>
       </c>
@@ -7349,10 +7323,10 @@
       <c r="E341" s="2"/>
       <c r="F341" s="2"/>
       <c r="G341" s="2">
-        <v>3035</v>
-      </c>
-    </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2061</v>
+      </c>
+    </row>
+    <row r="342" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
         <v>599</v>
       </c>
@@ -7362,10 +7336,10 @@
       <c r="E342" s="2"/>
       <c r="F342" s="2"/>
       <c r="G342" s="2">
-        <v>3038</v>
-      </c>
-    </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3010</v>
+      </c>
+    </row>
+    <row r="343" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
         <v>600</v>
       </c>
@@ -7375,96 +7349,32 @@
       <c r="E343" s="2"/>
       <c r="F343" s="2"/>
       <c r="G343" s="2">
-        <v>3042</v>
-      </c>
-    </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A344" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="B344" s="2"/>
-      <c r="C344" s="2"/>
-      <c r="D344" s="2"/>
-      <c r="E344" s="2"/>
-      <c r="F344" s="2"/>
-      <c r="G344" s="2">
-        <v>3100</v>
-      </c>
-    </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A345" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="B345" s="2"/>
-      <c r="C345" s="2"/>
-      <c r="D345" s="2"/>
-      <c r="E345" s="2"/>
-      <c r="F345" s="2"/>
-      <c r="G345" s="2">
-        <v>3105</v>
-      </c>
-    </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A346" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="B346" s="2"/>
-      <c r="C346" s="2"/>
-      <c r="D346" s="2"/>
-      <c r="E346" s="2"/>
-      <c r="F346" s="2"/>
-      <c r="G346" s="2">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A347" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="B347" s="2"/>
-      <c r="C347" s="2"/>
-      <c r="D347" s="2"/>
-      <c r="E347" s="2"/>
-      <c r="F347" s="2"/>
-      <c r="G347" s="2">
-        <v>2061</v>
-      </c>
-    </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A348" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="B348" s="2"/>
-      <c r="C348" s="2"/>
-      <c r="D348" s="2"/>
-      <c r="E348" s="2"/>
-      <c r="F348" s="2"/>
-      <c r="G348" s="2">
-        <v>3010</v>
-      </c>
-    </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A349" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="B349" s="2"/>
-      <c r="C349" s="2"/>
-      <c r="D349" s="2"/>
-      <c r="E349" s="2"/>
-      <c r="F349" s="2"/>
-      <c r="G349" s="2">
         <v>3061</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G301" xr:uid="{815B0988-14A5-456C-8EC4-0B80569E1D54}"/>
+  <autoFilter ref="A1:G343" xr:uid="{815B0988-14A5-456C-8EC4-0B80569E1D54}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="AI2R01_2G"/>
+        <filter val="AI2R01_3G"/>
+        <filter val="AI2R01_4G"/>
+        <filter val="ROM292_2G"/>
+        <filter val="ROM292_3G"/>
+        <filter val="ROM292_4G"/>
+        <filter val="ROM421_2G"/>
+        <filter val="ROM421_3G"/>
+        <filter val="ROM421_4G"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A577F19C-6F28-4FB3-9549-E0634C542BFC}">
-  <dimension ref="A1:D118"/>
+  <dimension ref="A1:D116"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" customWidth="1"/>
@@ -8597,7 +8507,7 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="B103">
         <v>33.560099999999998</v>
@@ -8608,7 +8518,7 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="B104">
         <v>33.573700000000002</v>
@@ -8619,7 +8529,7 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="B105">
         <v>33.566699999999997</v>
@@ -8630,7 +8540,7 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="B106">
         <v>33.6723</v>
@@ -8641,7 +8551,7 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="B107">
         <v>33.677599999999998</v>
@@ -8652,7 +8562,7 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="B108">
         <v>33.626200000000004</v>
@@ -8663,7 +8573,7 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="B109">
         <v>33.590699999999998</v>
@@ -8674,7 +8584,7 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="B110">
         <v>33.561700000000002</v>
@@ -8685,7 +8595,7 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="B111">
         <v>33.6877</v>
@@ -8696,7 +8606,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="B112">
         <v>33.676500000000004</v>
@@ -8707,7 +8617,7 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="B113">
         <v>33.678200000000004</v>
@@ -8718,7 +8628,7 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="B114">
         <v>33.613100000000003</v>
@@ -8729,7 +8639,7 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="B115">
         <v>33.660600000000002</v>
@@ -8740,7 +8650,7 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="B116">
         <v>33.682400000000001</v>
@@ -8749,30 +8659,8 @@
         <v>72.790299999999988</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>621</v>
-      </c>
-      <c r="B117">
-        <v>33.590699999999998</v>
-      </c>
-      <c r="C117">
-        <v>72.873699999999999</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>622</v>
-      </c>
-      <c r="B118">
-        <v>33.590699999999998</v>
-      </c>
-      <c r="C118">
-        <v>72.873699999999999</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D102" xr:uid="{A577F19C-6F28-4FB3-9549-E0634C542BFC}"/>
+  <autoFilter ref="A1:D116" xr:uid="{A577F19C-6F28-4FB3-9549-E0634C542BFC}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter>&amp;C_x000D_&amp;1#&amp;"Arial"&amp;9&amp;KA6A6A6 Sensitivity: Internal</oddFooter>
@@ -9043,7 +8931,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="B33" t="s">
         <v>0</v>
@@ -9051,7 +8939,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="B34" t="s">
         <v>0</v>
@@ -9068,7 +8956,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{805317FA-FB94-4097-B320-9A9B16478758}">
-  <dimension ref="A1:G148"/>
+  <dimension ref="A1:G146"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -12000,13 +11888,13 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="B128" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="C128" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="D128" s="4">
         <v>33.654499999999999</v>
@@ -12023,65 +11911,65 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="B129" t="s">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="C129" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="D129" s="4">
-        <v>33.590699999999998</v>
+        <v>33.6877</v>
       </c>
       <c r="E129" s="4">
-        <v>72.873699999999999</v>
+        <v>72.831199999999995</v>
       </c>
       <c r="F129" s="4">
-        <v>33.590699999999998</v>
+        <v>33.677599999999998</v>
       </c>
       <c r="G129" s="4">
-        <v>72.873699999999999</v>
+        <v>72.8125</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="B130" t="s">
-        <v>615</v>
+        <v>601</v>
       </c>
       <c r="C130" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="D130" s="4">
-        <v>33.6877</v>
+        <v>33.560099999999998</v>
       </c>
       <c r="E130" s="4">
-        <v>72.831199999999995</v>
+        <v>72.823000000000008</v>
       </c>
       <c r="F130" s="4">
-        <v>33.677599999999998</v>
+        <v>33.590699999999998</v>
       </c>
       <c r="G130" s="4">
-        <v>72.8125</v>
+        <v>72.873699999999999</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="B131" t="s">
+        <v>602</v>
+      </c>
+      <c r="C131" t="s">
         <v>607</v>
       </c>
-      <c r="C131" t="s">
-        <v>613</v>
-      </c>
       <c r="D131" s="4">
-        <v>33.560099999999998</v>
+        <v>33.573700000000002</v>
       </c>
       <c r="E131" s="4">
-        <v>72.823000000000008</v>
+        <v>72.862899999999996</v>
       </c>
       <c r="F131" s="4">
         <v>33.590699999999998</v>
@@ -12092,19 +11980,19 @@
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="B132" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="C132" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="D132" s="4">
-        <v>33.573700000000002</v>
+        <v>33.566699999999997</v>
       </c>
       <c r="E132" s="4">
-        <v>72.862899999999996</v>
+        <v>72.843099999999993</v>
       </c>
       <c r="F132" s="4">
         <v>33.590699999999998</v>
@@ -12115,19 +12003,19 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="B133" t="s">
-        <v>622</v>
+        <v>608</v>
       </c>
       <c r="C133" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="D133" s="4">
-        <v>33.590699999999998</v>
+        <v>33.561700000000002</v>
       </c>
       <c r="E133" s="4">
-        <v>72.873699999999999</v>
+        <v>72.838699999999989</v>
       </c>
       <c r="F133" s="4">
         <v>33.590699999999998</v>
@@ -12138,42 +12026,42 @@
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="B134" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="C134" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="D134" s="4">
-        <v>33.566699999999997</v>
+        <v>33.660600000000002</v>
       </c>
       <c r="E134" s="4">
-        <v>72.843099999999993</v>
+        <v>72.854600000000005</v>
       </c>
       <c r="F134" s="4">
-        <v>33.590699999999998</v>
+        <v>33.677599999999998</v>
       </c>
       <c r="G134" s="4">
-        <v>72.873699999999999</v>
+        <v>72.8125</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="B135" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C135" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="D135" s="4">
-        <v>33.561700000000002</v>
+        <v>33.613100000000003</v>
       </c>
       <c r="E135" s="4">
-        <v>72.838699999999989</v>
+        <v>72.86869999999999</v>
       </c>
       <c r="F135" s="4">
         <v>33.590699999999998</v>
@@ -12184,19 +12072,19 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="B136" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="C136" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="D136" s="4">
-        <v>33.660600000000002</v>
+        <v>33.678200000000004</v>
       </c>
       <c r="E136" s="4">
-        <v>72.854600000000005</v>
+        <v>72.823099999999997</v>
       </c>
       <c r="F136" s="4">
         <v>33.677599999999998</v>
@@ -12207,134 +12095,134 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="B137" t="s">
-        <v>618</v>
+        <v>604</v>
       </c>
       <c r="C137" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="D137" s="4">
-        <v>33.613100000000003</v>
+        <v>33.6723</v>
       </c>
       <c r="E137" s="4">
-        <v>72.86869999999999</v>
+        <v>72.756399999999999</v>
       </c>
       <c r="F137" s="4">
-        <v>33.590699999999998</v>
+        <v>33.677599999999998</v>
       </c>
       <c r="G137" s="4">
-        <v>72.873699999999999</v>
+        <v>72.8125</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="B138" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="C138" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="D138" s="4">
-        <v>33.678200000000004</v>
+        <v>33.677599999999998</v>
       </c>
       <c r="E138" s="4">
-        <v>72.823099999999997</v>
+        <v>72.8125</v>
       </c>
       <c r="F138" s="4">
-        <v>33.677599999999998</v>
+        <v>33.626200000000004</v>
       </c>
       <c r="G138" s="4">
-        <v>72.8125</v>
+        <v>72.850799999999992</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="B139" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="C139" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="D139" s="4">
-        <v>33.6723</v>
+        <v>33.626200000000004</v>
       </c>
       <c r="E139" s="4">
-        <v>72.756399999999999</v>
+        <v>72.850799999999992</v>
       </c>
       <c r="F139" s="4">
-        <v>33.677599999999998</v>
+        <v>33.590699999999998</v>
       </c>
       <c r="G139" s="4">
-        <v>72.8125</v>
+        <v>72.873699999999999</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="B140" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="C140" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="D140" s="4">
+        <v>33.682400000000001</v>
+      </c>
+      <c r="E140" s="4">
+        <v>72.790299999999988</v>
+      </c>
+      <c r="F140" s="4">
         <v>33.677599999999998</v>
       </c>
-      <c r="E140" s="4">
+      <c r="G140" s="4">
         <v>72.8125</v>
-      </c>
-      <c r="F140" s="4">
-        <v>33.626200000000004</v>
-      </c>
-      <c r="G140" s="4">
-        <v>72.850799999999992</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="B141" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="C141" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="D141" s="4">
-        <v>33.626200000000004</v>
+        <v>33.590699999999998</v>
       </c>
       <c r="E141" s="4">
-        <v>72.850799999999992</v>
+        <v>72.873699999999999</v>
       </c>
       <c r="F141" s="4">
-        <v>33.590699999999998</v>
+        <v>33.596299999999999</v>
       </c>
       <c r="G141" s="4">
-        <v>72.873699999999999</v>
+        <v>72.81689999999999</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="B142" t="s">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="C142" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="D142" s="4">
-        <v>33.682400000000001</v>
+        <v>33.676500000000004</v>
       </c>
       <c r="E142" s="4">
-        <v>72.790299999999988</v>
+        <v>72.852799999999988</v>
       </c>
       <c r="F142" s="4">
         <v>33.677599999999998</v>
@@ -12345,144 +12233,98 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="B143" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C143" t="s">
-        <v>624</v>
+        <v>607</v>
       </c>
       <c r="D143" s="4">
+        <v>33.654499999999999</v>
+      </c>
+      <c r="E143" s="4">
+        <v>72.906599999999997</v>
+      </c>
+      <c r="F143" s="4">
         <v>33.590699999999998</v>
       </c>
-      <c r="E143" s="4">
+      <c r="G143" s="4">
         <v>72.873699999999999</v>
-      </c>
-      <c r="F143" s="4">
-        <v>33.596299999999999</v>
-      </c>
-      <c r="G143" s="4">
-        <v>72.81689999999999</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="B144" t="s">
-        <v>616</v>
+        <v>605</v>
       </c>
       <c r="C144" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="D144" s="4">
-        <v>33.676500000000004</v>
+        <v>33.677599999999998</v>
       </c>
       <c r="E144" s="4">
-        <v>72.852799999999988</v>
+        <v>72.8125</v>
       </c>
       <c r="F144" s="4">
-        <v>33.677599999999998</v>
+        <v>33.626200000000004</v>
       </c>
       <c r="G144" s="4">
-        <v>72.8125</v>
+        <v>72.850799999999992</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="B145" t="s">
-        <v>623</v>
+        <v>605</v>
       </c>
       <c r="C145" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="D145" s="4">
-        <v>33.654499999999999</v>
+        <v>33.677599999999998</v>
       </c>
       <c r="E145" s="4">
-        <v>72.906599999999997</v>
+        <v>72.8125</v>
       </c>
       <c r="F145" s="4">
-        <v>33.590699999999998</v>
+        <v>33.626200000000004</v>
       </c>
       <c r="G145" s="4">
-        <v>72.873699999999999</v>
+        <v>72.850799999999992</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="B146" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="C146" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="D146" s="4">
-        <v>33.677599999999998</v>
+        <v>33.626200000000004</v>
       </c>
       <c r="E146" s="4">
-        <v>72.8125</v>
+        <v>72.850799999999992</v>
       </c>
       <c r="F146" s="4">
-        <v>33.626200000000004</v>
+        <v>33.590699999999998</v>
       </c>
       <c r="G146" s="4">
-        <v>72.850799999999992</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>644</v>
-      </c>
-      <c r="B147" t="s">
-        <v>611</v>
-      </c>
-      <c r="C147" t="s">
-        <v>612</v>
-      </c>
-      <c r="D147" s="4">
-        <v>33.677599999999998</v>
-      </c>
-      <c r="E147" s="4">
-        <v>72.8125</v>
-      </c>
-      <c r="F147" s="4">
-        <v>33.626200000000004</v>
-      </c>
-      <c r="G147" s="4">
-        <v>72.850799999999992</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>645</v>
-      </c>
-      <c r="B148" t="s">
-        <v>612</v>
-      </c>
-      <c r="C148" t="s">
-        <v>613</v>
-      </c>
-      <c r="D148" s="4">
-        <v>33.626200000000004</v>
-      </c>
-      <c r="E148" s="4">
-        <v>72.850799999999992</v>
-      </c>
-      <c r="F148" s="4">
-        <v>33.590699999999998</v>
-      </c>
-      <c r="G148" s="4">
         <v>72.873699999999999</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G127" xr:uid="{805317FA-FB94-4097-B320-9A9B16478758}"/>
+  <autoFilter ref="A1:G146" xr:uid="{805317FA-FB94-4097-B320-9A9B16478758}"/>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -12604,10 +12446,10 @@
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>613</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="A8" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>15</v>
       </c>
     </row>
